--- a/data/trans_orig/P57B1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido deprimido en 2023</t>
+          <t>Población según se ha sentido deprimido en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>33870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>41838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62333</t>
+          <t>62393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63909</t>
+          <t>62964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90337</t>
+          <t>90400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51031</t>
+          <t>49377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76409</t>
+          <t>77170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104582</t>
+          <t>102223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>131656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161052</t>
+          <t>161258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200654</t>
+          <t>199780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>150420</t>
+          <t>149120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>189540</t>
+          <t>185899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>291995</t>
+          <t>288951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333822</t>
+          <t>333346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>451635</t>
+          <t>450495</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>509808</t>
+          <t>508002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235959</t>
+          <t>238308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279034</t>
+          <t>280520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>249297</t>
+          <t>249806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>290737</t>
+          <t>290942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>498186</t>
+          <t>498227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>556618</t>
+          <t>558776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>23838</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50603</t>
+          <t>51904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53691</t>
+          <t>53742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58613</t>
+          <t>58277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95799</t>
+          <t>94574</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>66265</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120999</t>
+          <t>121000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89009</t>
+          <t>92101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149173</t>
+          <t>153482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175760</t>
+          <t>179413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260771</t>
+          <t>259446</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>418058</t>
+          <t>426880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>686006</t>
+          <t>683801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>728401</t>
+          <t>720884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1318159</t>
+          <t>1238187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249175</t>
+          <t>1244139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1950243</t>
+          <t>1909381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1445007</t>
+          <t>1447097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1774834</t>
+          <t>1764259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>815371</t>
+          <t>866151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1328315</t>
+          <t>1339537</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2372940</t>
+          <t>2371999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2998600</t>
+          <t>3000860</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>25580</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26470</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>53126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>38514</t>
+          <t>39680</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67926</t>
+          <t>67590</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155242</t>
+          <t>154098</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202797</t>
+          <t>201701</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164632</t>
+          <t>163941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204924</t>
+          <t>204050</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>330815</t>
+          <t>330252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393282</t>
+          <t>394225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417250</t>
+          <t>419393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468269</t>
+          <t>467046</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>409841</t>
+          <t>410165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>452715</t>
+          <t>453641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>842437</t>
+          <t>845162</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>910331</t>
+          <t>911721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>52118</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87080</t>
+          <t>87913</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76531</t>
+          <t>80054</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>115965</t>
+          <t>117912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138861</t>
+          <t>140459</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>192698</t>
+          <t>194302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138856</t>
+          <t>141022</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207033</t>
+          <t>208194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231918</t>
+          <t>228267</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311113</t>
+          <t>308918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>392606</t>
+          <t>387852</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501834</t>
+          <t>502667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>734064</t>
+          <t>726726</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1034216</t>
+          <t>1035665</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1218093</t>
+          <t>1218635</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1760677</t>
+          <t>1769709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2099828</t>
+          <t>2096392</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2774509</t>
+          <t>2804271</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2145420</t>
+          <t>2139340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2527805</t>
+          <t>2542081</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1580643</t>
+          <t>1568009</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2034462</t>
+          <t>2032573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3812377</t>
+          <t>3776791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4417844</t>
+          <t>4417253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>18328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33870</t>
+          <t>36464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51381</t>
+          <t>58533</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41838</t>
+          <t>47881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62393</t>
+          <t>70360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75588</t>
+          <t>84543</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62964</t>
+          <t>70300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90400</t>
+          <t>100562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>70294</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49377</t>
+          <t>56753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>84771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>117034</t>
+          <t>129048</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102223</t>
+          <t>113653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131656</t>
+          <t>145241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>179663</t>
+          <t>199342</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161258</t>
+          <t>179429</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199780</t>
+          <t>221074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>168101</t>
+          <t>186528</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149120</t>
+          <t>162638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>185899</t>
+          <t>207440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>311269</t>
+          <t>339239</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>288951</t>
+          <t>316963</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333346</t>
+          <t>360426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>479370</t>
+          <t>525767</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>450495</t>
+          <t>493131</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>508002</t>
+          <t>555654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>258598</t>
+          <t>294138</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238308</t>
+          <t>272181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>318101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>269635</t>
+          <t>288704</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>249806</t>
+          <t>268275</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>290942</t>
+          <t>310749</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>528233</t>
+          <t>582842</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>498227</t>
+          <t>549385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>558776</t>
+          <t>616119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>513535</t>
+          <t>576970</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>513535</t>
+          <t>576970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>513535</t>
+          <t>576970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>749320</t>
+          <t>815524</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>749320</t>
+          <t>815524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749320</t>
+          <t>815524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1262855</t>
+          <t>1392494</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1262855</t>
+          <t>1392494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1262855</t>
+          <t>1392494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36632</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23838</t>
+          <t>30517</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51904</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>32556</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53742</t>
+          <t>58111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>75781</t>
+          <t>85937</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58277</t>
+          <t>69911</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>94574</t>
+          <t>107527</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>99056</t>
+          <t>109954</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66265</t>
+          <t>90515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121000</t>
+          <t>132585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>124911</t>
+          <t>143318</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92101</t>
+          <t>124267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153482</t>
+          <t>164001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>223967</t>
+          <t>253272</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179413</t>
+          <t>225843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>259446</t>
+          <t>285675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>594012</t>
+          <t>669473</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>426880</t>
+          <t>626111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>683801</t>
+          <t>717041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>883526</t>
+          <t>768248</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>720884</t>
+          <t>728206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1238187</t>
+          <t>813834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1477538</t>
+          <t>1437721</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1244139</t>
+          <t>1371415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1909381</t>
+          <t>1502783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1554288</t>
+          <t>1403319</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1447097</t>
+          <t>1352892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1764259</t>
+          <t>1451459</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1187248</t>
+          <t>1212141</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>866151</t>
+          <t>1168384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1339537</t>
+          <t>1253347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2741536</t>
+          <t>2615459</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2371999</t>
+          <t>2545207</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3000860</t>
+          <t>2682191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2283988</t>
+          <t>2224138</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2283988</t>
+          <t>2224138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2283988</t>
+          <t>2224138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2234834</t>
+          <t>2168252</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2234834</t>
+          <t>2168252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2234834</t>
+          <t>2168252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4518822</t>
+          <t>4392389</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4518822</t>
+          <t>4392389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4518822</t>
+          <t>4392389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>29882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15654</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>32400</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36277</t>
+          <t>38542</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>28064</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53126</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>51932</t>
+          <t>57541</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>44473</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67590</t>
+          <t>73127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>197319</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>154098</t>
+          <t>173218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>201701</t>
+          <t>225086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>183403</t>
+          <t>204237</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163941</t>
+          <t>183174</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204050</t>
+          <t>226636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>361723</t>
+          <t>401556</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>330252</t>
+          <t>370507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>394225</t>
+          <t>436006</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>443687</t>
+          <t>484986</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419393</t>
+          <t>456703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467046</t>
+          <t>510926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>432554</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>410165</t>
+          <t>456513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>453641</t>
+          <t>503687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>876241</t>
+          <t>966474</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845162</t>
+          <t>929772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>911721</t>
+          <t>1002675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>645607</t>
+          <t>710608</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>645607</t>
+          <t>710608</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>645607</t>
+          <t>710608</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1305331</t>
+          <t>1444739</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1305331</t>
+          <t>1444739</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1305331</t>
+          <t>1444739</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>76707</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>60543</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87913</t>
+          <t>94697</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>98020</t>
+          <t>112942</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80054</t>
+          <t>96720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117912</t>
+          <t>132043</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>166805</t>
+          <t>189648</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>140459</t>
+          <t>166650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>194302</t>
+          <t>216901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>177339</t>
+          <t>199246</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141022</t>
+          <t>173041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208194</t>
+          <t>226372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>278223</t>
+          <t>310909</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228267</t>
+          <t>283586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308918</t>
+          <t>340150</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>455562</t>
+          <t>510155</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>387852</t>
+          <t>472500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502667</t>
+          <t>553976</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>940432</t>
+          <t>1053321</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>726726</t>
+          <t>996764</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1035665</t>
+          <t>1115714</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1378198</t>
+          <t>1311724</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1218635</t>
+          <t>1260890</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1769709</t>
+          <t>1364991</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2318631</t>
+          <t>2365044</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2096392</t>
+          <t>2284479</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2804271</t>
+          <t>2438035</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2256573</t>
+          <t>2182442</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2139340</t>
+          <t>2118859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2542081</t>
+          <t>2240723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1889437</t>
+          <t>1982334</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1568009</t>
+          <t>1927114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2032573</t>
+          <t>2037949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4146010</t>
+          <t>4164776</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3776791</t>
+          <t>4085125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4417253</t>
+          <t>4250654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>58,79%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3443130</t>
+          <t>3511715</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3443130</t>
+          <t>3511715</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3443130</t>
+          <t>3511715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3643877</t>
+          <t>3717908</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3643877</t>
+          <t>3717908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3643877</t>
+          <t>3717908</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7087008</t>
+          <t>7229623</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7087008</t>
+          <t>7229623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7087008</t>
+          <t>7229623</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
